--- a/data/trans_orig/P1405-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1405-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colitis en 2012</t>
+          <t>Población con diagnóstico de colitis en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3367</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17858</t>
+          <t>16770</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12073</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6638</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23801</t>
+          <t>22992</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>685611</t>
+          <t>686699</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>700102</t>
+          <t>700245</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>684977</t>
+          <t>685242</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>695032</t>
+          <t>694992</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1376718</t>
+          <t>1377527</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1393881</t>
+          <t>1393107</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3123</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14819</t>
+          <t>15021</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11382</t>
+          <t>11369</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>30836</t>
+          <t>29324</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16831</t>
+          <t>16935</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37994</t>
+          <t>39075</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1003128</t>
+          <t>1002926</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1014824</t>
+          <t>1014862</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>996955</t>
+          <t>998467</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1016409</t>
+          <t>1016422</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2007744</t>
+          <t>2006663</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2028907</t>
+          <t>2028803</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15907</t>
+          <t>15119</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6498</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21264</t>
+          <t>20913</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11453</t>
+          <t>11385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29401</t>
+          <t>30393</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>741716</t>
+          <t>742504</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754689</t>
+          <t>754740</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>755910</t>
+          <t>756261</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>770676</t>
+          <t>770914</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1505396</t>
+          <t>1504404</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523344</t>
+          <t>1523412</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>2035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>14485</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16896</t>
+          <t>16869</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40047</t>
+          <t>38039</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21687</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46462</t>
+          <t>47643</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>932629</t>
+          <t>933254</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>945805</t>
+          <t>945704</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1011854</t>
+          <t>1013862</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1035005</t>
+          <t>1035032</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1953178</t>
+          <t>1951997</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1977953</t>
+          <t>1978116</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19126</t>
+          <t>18935</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42085</t>
+          <t>42327</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47824</t>
+          <t>46485</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80268</t>
+          <t>79684</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>73653</t>
+          <t>71252</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113629</t>
+          <t>110948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3384694</t>
+          <t>3384452</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3407653</t>
+          <t>3407844</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3473648</t>
+          <t>3474232</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3506092</t>
+          <t>3507431</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6867065</t>
+          <t>6869746</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6907041</t>
+          <t>6909442</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colitis en 2016</t>
+          <t>Población con diagnóstico de colitis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9710</t>
+          <t>9873</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20357</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8786</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24204</t>
+          <t>23783</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>665090</t>
+          <t>664927</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>652482</t>
+          <t>652447</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>666384</t>
+          <t>666597</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1323435</t>
+          <t>1323856</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1338853</t>
+          <t>1339073</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2921</t>
+          <t>2882</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13898</t>
+          <t>12836</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6889</t>
+          <t>7498</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23691</t>
+          <t>24017</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13172</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32211</t>
+          <t>32703</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1008533</t>
+          <t>1009595</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1019510</t>
+          <t>1019549</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1019222</t>
+          <t>1018896</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1036024</t>
+          <t>1035415</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2033133</t>
+          <t>2032641</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2052172</t>
+          <t>2052182</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12050</t>
+          <t>12455</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>2962</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14462</t>
+          <t>14339</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7111</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21856</t>
+          <t>22772</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>747502</t>
+          <t>747097</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>757470</t>
+          <t>757534</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>770549</t>
+          <t>770672</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>782029</t>
+          <t>782049</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1522707</t>
+          <t>1521791</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1537452</t>
+          <t>1537420</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4594</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20583</t>
+          <t>17909</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34410</t>
+          <t>35152</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21624</t>
+          <t>21741</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47000</t>
+          <t>46768</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>916984</t>
+          <t>919658</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>932973</t>
+          <t>933130</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1009369</t>
+          <t>1008627</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1029866</t>
+          <t>1029608</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1934346</t>
+          <t>1934578</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1959722</t>
+          <t>1959605</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16236</t>
+          <t>15738</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40427</t>
+          <t>37674</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41414</t>
+          <t>41740</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>72720</t>
+          <t>73977</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,47 +4100,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>1,18%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>81136</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>62648</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>100946</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>1,17%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,05%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>81136</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>64884</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>99993</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3353923</t>
+          <t>3356676</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3378114</t>
+          <t>3378612</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3471822</t>
+          <t>3470565</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3503128</t>
+          <t>3502802</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,47 +4213,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>98,82%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>6496</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6857756</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6837946</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6876244</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>98,83%</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>6496</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6857756</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6838899</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6874008</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1405-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1405-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3307</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>16905</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>1985</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11808</t>
+          <t>12052</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7412</t>
+          <t>7516</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22992</t>
+          <t>23833</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>686699</t>
+          <t>686564</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>700245</t>
+          <t>700162</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>685242</t>
+          <t>684998</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>694992</t>
+          <t>695065</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1377527</t>
+          <t>1376686</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1393107</t>
+          <t>1393003</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>3087</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15021</t>
+          <t>14581</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11369</t>
+          <t>10955</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29324</t>
+          <t>29548</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16935</t>
+          <t>18156</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>39075</t>
+          <t>38687</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1002926</t>
+          <t>1003366</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1014862</t>
+          <t>1014860</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>998467</t>
+          <t>998243</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1016422</t>
+          <t>1016836</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2006663</t>
+          <t>2007051</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2028803</t>
+          <t>2027582</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2883</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15119</t>
+          <t>14842</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20913</t>
+          <t>20586</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11385</t>
+          <t>11071</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30393</t>
+          <t>29100</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>742504</t>
+          <t>742781</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754740</t>
+          <t>755514</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>756261</t>
+          <t>756588</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>770914</t>
+          <t>770997</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1504404</t>
+          <t>1505697</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1523412</t>
+          <t>1523726</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2035</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14485</t>
+          <t>15639</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16869</t>
+          <t>16752</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38039</t>
+          <t>39977</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21524</t>
+          <t>22168</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>47643</t>
+          <t>46147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>933254</t>
+          <t>932100</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>945704</t>
+          <t>945770</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1013862</t>
+          <t>1011924</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1035032</t>
+          <t>1035149</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1951997</t>
+          <t>1953493</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1978116</t>
+          <t>1977472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18935</t>
+          <t>18807</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42327</t>
+          <t>42315</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2123,7 +2123,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>46485</t>
+          <t>47695</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79684</t>
+          <t>81547</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,47 +2153,47 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>91495</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>72854</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>113983</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>91495</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>71252</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>110948</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3384452</t>
+          <t>3384464</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3407844</t>
+          <t>3407972</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3474232</t>
+          <t>3472369</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3507431</t>
+          <t>3506221</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,47 +2266,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>6423</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6889199</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6866711</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6907840</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>98,69%</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>6423</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6889199</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6869746</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6909442</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9873</t>
+          <t>9372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6782</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20392</t>
+          <t>21297</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>8389</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23783</t>
+          <t>24604</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>664927</t>
+          <t>665428</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>652447</t>
+          <t>651542</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>666597</t>
+          <t>666057</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1323856</t>
+          <t>1323035</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1339073</t>
+          <t>1339250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12836</t>
+          <t>13989</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7498</t>
+          <t>7472</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24017</t>
+          <t>22853</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13162</t>
+          <t>13165</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32703</t>
+          <t>31939</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1009595</t>
+          <t>1008442</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1019549</t>
+          <t>1019448</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1018896</t>
+          <t>1020060</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1035415</t>
+          <t>1035441</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2032641</t>
+          <t>2033405</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2052182</t>
+          <t>2052179</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12455</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2962</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14339</t>
+          <t>14733</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22772</t>
+          <t>22615</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>747097</t>
+          <t>747531</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>757534</t>
+          <t>757447</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>770672</t>
+          <t>770278</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>782049</t>
+          <t>781923</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1521791</t>
+          <t>1521948</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1537420</t>
+          <t>1537739</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4596</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>18479</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14171</t>
+          <t>14443</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35152</t>
+          <t>34320</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21741</t>
+          <t>22241</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>46768</t>
+          <t>50031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>919658</t>
+          <t>919088</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>933130</t>
+          <t>932971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,53%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1008627</t>
+          <t>1009459</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1029608</t>
+          <t>1029336</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1934578</t>
+          <t>1931315</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1959605</t>
+          <t>1959105</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,88%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>16462</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37674</t>
+          <t>37841</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>41740</t>
+          <t>42015</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>73977</t>
+          <t>73727</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62648</t>
+          <t>65212</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>100946</t>
+          <t>102598</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3356676</t>
+          <t>3356509</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3378612</t>
+          <t>3377888</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3470565</t>
+          <t>3470815</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3502802</t>
+          <t>3502527</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6837946</t>
+          <t>6836294</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6876244</t>
+          <t>6873680</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
